--- a/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsBuildSchemeList.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsBuildSchemeList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-sp\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2B0326-E491-48E6-8A8A-7492E790C3FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CAD6E50-DA4D-466D-8A49-118A5D5EA7AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5388" yWindow="4416" windowWidth="23040" windowHeight="12264" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023-07-05" sheetId="1" r:id="rId1"/>
@@ -22,10 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
-    <t>方案名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>变更类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -46,15 +42,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>施工重难点</t>
+    <t>方案类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*施工重难点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*方案名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>注：wbs编号和wbs名称如果有多个，按逗号（,）分割</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>方案类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -62,7 +62,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -100,6 +100,14 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -150,7 +158,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -168,6 +176,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -453,48 +467,60 @@
     <col min="4" max="5" width="17.6640625" customWidth="1"/>
     <col min="6" max="6" width="11.109375" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" customWidth="1"/>
+    <col min="8" max="8" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
+      <c r="A2" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="C2" s="4"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="I7" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I7" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="1">
+  <dataValidations count="5">
     <dataValidation showInputMessage="1" showErrorMessage="1" sqref="A1:A1048576" xr:uid="{8C7B18EB-1706-4693-9E43-8A9FE2C13F13}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{A5FEE78C-64D3-4213-AFF1-516EF2DCDDCC}">
+      <formula1>"推迟,提前,新增,废止"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{C2C33710-E668-4205-A982-FC02DD950583}">
+      <formula1>"项目总体与临时工程,爆破工程,绿化工程,照明工程,设备安拆,建筑主体结构,建筑屋面,建筑给排水及采暖,建筑装饰装修,建筑电气工程,建筑防水,建筑附属设施,智能建筑,交通工程,地基与基础,路基工程,路面工程,边坡工程,交通机电及附属设施,轨道工程,电力管沟工程,给排水管道工程,机场机库,机场跑道,机场停机坪,机场航站楼,机场行李系统,旅客服务设施,简支桥梁,连续桥梁,拱桥、斜拉桥、悬索桥,盾构,防排水工程,隧道工程,涵洞、通道,围堰,钢栈桥,疏浚与吹填工程,航道治理工程,码头与岸壁工程,防波堤护岸工程,其他"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F1048576" xr:uid="{A2CFE391-003B-4E7D-8B17-88BD2C035E16}">
+      <formula1>"Ⅰ,Ⅱ,Ⅲ,Ⅳ"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576" xr:uid="{3F6E782B-132D-4291-996A-5A482D0F5A7E}">
+      <formula1>"危大,超危大,一般"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsBuildSchemeList.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsBuildSchemeList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-sp\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CAD6E50-DA4D-466D-8A49-118A5D5EA7AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43BC21B9-4355-493C-824D-1C30C6C1C843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,20 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>变更类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>关联wbs编号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>关联wbs名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>方案分级</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -46,15 +38,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>*施工重难点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*方案名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>注：wbs编号和wbs名称如果有多个，按逗号（,）分割</t>
+    <t>*施工重难点（必填）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*方案名称（必填）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关联wbs编号（多个用,分割）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关联wbs名称（多个用,分割）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -104,7 +100,7 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF990033"/>
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
@@ -177,10 +173,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -189,6 +185,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF990033"/>
+      <color rgb="FFCC3300"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -461,45 +463,44 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" customWidth="1"/>
-    <col min="4" max="5" width="17.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" customWidth="1"/>
+    <col min="1" max="1" width="25.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="33.5546875" customWidth="1"/>
+    <col min="4" max="4" width="28.77734375" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" customWidth="1"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>7</v>
+      <c r="A1" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="7" t="s">
         <v>4</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="A2" s="4"/>
       <c r="C2" s="4"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">

--- a/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsBuildSchemeList.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsBuildSchemeList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-sp\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43BC21B9-4355-493C-824D-1C30C6C1C843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BBC7F90-9183-4323-BD54-706A4F172C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023-07-05" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>变更类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -51,6 +51,10 @@
   </si>
   <si>
     <t>关联wbs名称（多个用,分割）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*计划实施时间（必填）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -58,6 +62,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -154,7 +161,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -170,14 +177,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -461,20 +474,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="25.88671875" customWidth="1"/>
+    <col min="1" max="1" width="25.875" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="33.5546875" customWidth="1"/>
-    <col min="4" max="4" width="28.77734375" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" customWidth="1"/>
-    <col min="6" max="6" width="12.77734375" customWidth="1"/>
-    <col min="7" max="7" width="21.44140625" customWidth="1"/>
+    <col min="3" max="3" width="33.5" customWidth="1"/>
+    <col min="4" max="4" width="28.75" customWidth="1"/>
+    <col min="5" max="5" width="13.5" customWidth="1"/>
+    <col min="6" max="6" width="12.75" customWidth="1"/>
+    <col min="7" max="7" width="21.5" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
+    <col min="9" max="9" width="23.5" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -495,20 +509,23 @@
       <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
+      <c r="I1" s="7" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="13.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4"/>
       <c r="C2" s="4"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="I7" s="5"/>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I7" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation showInputMessage="1" showErrorMessage="1" sqref="A1:A1048576" xr:uid="{8C7B18EB-1706-4693-9E43-8A9FE2C13F13}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{A5FEE78C-64D3-4213-AFF1-516EF2DCDDCC}">
       <formula1>"推迟,提前,新增,废止"</formula1>
@@ -522,6 +539,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576" xr:uid="{3F6E782B-132D-4291-996A-5A482D0F5A7E}">
       <formula1>"危大,超危大,一般"</formula1>
     </dataValidation>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I1048576" xr:uid="{7885542F-F144-4DE7-A84C-251C7BFEC892}">
+      <formula1>1949</formula1>
+      <formula2>367342</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsBuildSchemeList.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsBuildSchemeList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-sp\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BBC7F90-9183-4323-BD54-706A4F172C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A7E80B-2EA5-4EE6-84D9-C471A586A3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023-07-05" sheetId="1" r:id="rId1"/>
@@ -30,10 +30,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>是否危大工程</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>方案类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -56,6 +52,9 @@
   <si>
     <t>*计划实施时间（必填）</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>危大</t>
   </si>
 </sst>
 </file>
@@ -63,7 +62,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -183,13 +182,13 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -474,53 +473,53 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.875" customWidth="1"/>
+    <col min="1" max="1" width="25.88671875" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="33.5" customWidth="1"/>
-    <col min="4" max="4" width="28.75" customWidth="1"/>
-    <col min="5" max="5" width="13.5" customWidth="1"/>
-    <col min="6" max="6" width="12.75" customWidth="1"/>
-    <col min="7" max="7" width="21.5" customWidth="1"/>
+    <col min="3" max="3" width="33.44140625" customWidth="1"/>
+    <col min="4" max="4" width="28.77734375" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="9" width="23.5" style="8" customWidth="1"/>
+    <col min="9" max="9" width="23.44140625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="E1" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="13.9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:9" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="C2" s="4"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I7" s="9"/>
     </row>
   </sheetData>
@@ -537,7 +536,7 @@
       <formula1>"Ⅰ,Ⅱ,Ⅲ,Ⅳ"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576" xr:uid="{3F6E782B-132D-4291-996A-5A482D0F5A7E}">
-      <formula1>"危大,超危大,一般"</formula1>
+      <formula1>"一般,危大,超危大"</formula1>
     </dataValidation>
     <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I1048576" xr:uid="{7885542F-F144-4DE7-A84C-251C7BFEC892}">
       <formula1>1949</formula1>

--- a/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsBuildSchemeList.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsBuildSchemeList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-sp\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A7E80B-2EA5-4EE6-84D9-C471A586A3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20322ECA-300C-42A7-B52E-A4599610EAD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>变更类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -30,18 +30,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>方案类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*施工重难点（必填）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*方案名称（必填）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>关联wbs编号（多个用,分割）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -50,11 +38,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>*计划实施时间（必填）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>危大</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方案名称（必填）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施工重难点（必填）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>变更计划实施时间
+（版本调整时必填）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划实施时间
+（版本V1.0时必填）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>原计划实施时间
+（版本调整时可填）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -160,13 +168,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -182,14 +187,23 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -472,75 +486,76 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.88671875" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="33.44140625" customWidth="1"/>
     <col min="4" max="4" width="28.77734375" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" customWidth="1"/>
-    <col min="6" max="6" width="12.77734375" customWidth="1"/>
-    <col min="7" max="7" width="21.44140625" customWidth="1"/>
-    <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="9" width="23.44140625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="8" max="8" width="23.44140625" style="6" customWidth="1"/>
+    <col min="9" max="10" width="26.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:10" ht="31.2" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>7</v>
       </c>
+      <c r="J1" s="11" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="C2" s="4"/>
+    <row r="2" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="I2" s="10"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="I7" s="9"/>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H7" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="6">
+  <dataValidations count="5">
     <dataValidation showInputMessage="1" showErrorMessage="1" sqref="A1:A1048576" xr:uid="{8C7B18EB-1706-4693-9E43-8A9FE2C13F13}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{A5FEE78C-64D3-4213-AFF1-516EF2DCDDCC}">
       <formula1>"推迟,提前,新增,废止"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{C2C33710-E668-4205-A982-FC02DD950583}">
-      <formula1>"项目总体与临时工程,爆破工程,绿化工程,照明工程,设备安拆,建筑主体结构,建筑屋面,建筑给排水及采暖,建筑装饰装修,建筑电气工程,建筑防水,建筑附属设施,智能建筑,交通工程,地基与基础,路基工程,路面工程,边坡工程,交通机电及附属设施,轨道工程,电力管沟工程,给排水管道工程,机场机库,机场跑道,机场停机坪,机场航站楼,机场行李系统,旅客服务设施,简支桥梁,连续桥梁,拱桥、斜拉桥、悬索桥,盾构,防排水工程,隧道工程,涵洞、通道,围堰,钢栈桥,疏浚与吹填工程,航道治理工程,码头与岸壁工程,防波堤护岸工程,其他"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F1048576" xr:uid="{A2CFE391-003B-4E7D-8B17-88BD2C035E16}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{A2CFE391-003B-4E7D-8B17-88BD2C035E16}">
       <formula1>"Ⅰ,Ⅱ,Ⅲ,Ⅳ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576" xr:uid="{3F6E782B-132D-4291-996A-5A482D0F5A7E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F1048576" xr:uid="{3F6E782B-132D-4291-996A-5A482D0F5A7E}">
       <formula1>"一般,危大,超危大"</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I1048576" xr:uid="{7885542F-F144-4DE7-A84C-251C7BFEC892}">
-      <formula1>1949</formula1>
-      <formula2>367342</formula2>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H1048576 I1:I1048576" xr:uid="{04CC7526-2AAB-4B71-A3DC-4971EBCC8533}">
+      <formula1>18172</formula1>
+      <formula2>383415</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsBuildSchemeList.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsBuildSchemeList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-sp\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20322ECA-300C-42A7-B52E-A4599610EAD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1418E965-B250-4F9E-BCB1-B7D799115398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023-07-05" sheetId="1" r:id="rId1"/>
@@ -38,18 +38,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>危大</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>方案名称（必填）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>施工重难点（必填）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>变更计划实施时间
 （版本调整时必填）</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -60,8 +48,20 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>原计划实施时间
-（版本调整时可填）</t>
+    <t>计划编制完成时间
+（版本调整时必填）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方案名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否危大工程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施工重难点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -134,7 +134,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -149,17 +149,12 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
+      <top style="thin">
         <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -168,41 +163,32 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -487,58 +473,58 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="25.88671875" customWidth="1"/>
+    <col min="1" max="1" width="25.875" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="33.44140625" customWidth="1"/>
-    <col min="4" max="4" width="28.77734375" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" customWidth="1"/>
-    <col min="6" max="6" width="21.44140625" customWidth="1"/>
+    <col min="3" max="3" width="33.5" customWidth="1"/>
+    <col min="4" max="4" width="28.75" customWidth="1"/>
+    <col min="5" max="5" width="12.75" customWidth="1"/>
+    <col min="6" max="6" width="21.5" customWidth="1"/>
     <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="23.44140625" style="6" customWidth="1"/>
-    <col min="9" max="10" width="26.109375" customWidth="1"/>
+    <col min="8" max="8" width="23.5" style="2" customWidth="1"/>
+    <col min="9" max="10" width="26.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="31.2" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:10" ht="33" x14ac:dyDescent="0.15">
+      <c r="A1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="I1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="J1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="2" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="I2" s="10"/>
+    <row r="2" spans="1:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="I2" s="4"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H7" s="7"/>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="H7" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -553,7 +539,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F1048576" xr:uid="{3F6E782B-132D-4291-996A-5A482D0F5A7E}">
       <formula1>"一般,危大,超危大"</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H1048576 I1:I1048576" xr:uid="{04CC7526-2AAB-4B71-A3DC-4971EBCC8533}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H1048576 I1:I1048576 J1:J1048576" xr:uid="{04CC7526-2AAB-4B71-A3DC-4971EBCC8533}">
       <formula1>18172</formula1>
       <formula2>383415</formula2>
     </dataValidation>

--- a/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsBuildSchemeList.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsBuildSchemeList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-sp\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1418E965-B250-4F9E-BCB1-B7D799115398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC93801E-5859-45D7-AD2A-DF6550564114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,10 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t>变更类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>方案分级</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -62,6 +58,11 @@
   </si>
   <si>
     <t>施工重难点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>变更类型
+（版本调整时填写）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -163,7 +164,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -189,6 +190,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -476,7 +480,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="25.875" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="2" max="2" width="20.125" customWidth="1"/>
     <col min="3" max="3" width="33.5" customWidth="1"/>
     <col min="4" max="4" width="28.75" customWidth="1"/>
     <col min="5" max="5" width="12.75" customWidth="1"/>
@@ -488,34 +492,34 @@
   <sheetData>
     <row r="1" spans="1:10" ht="33" x14ac:dyDescent="0.15">
       <c r="A1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="G1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="6" t="s">
+      <c r="J1" s="8" t="s">
         <v>5</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.15">
@@ -527,6 +531,7 @@
       <c r="H7" s="3"/>
     </row>
   </sheetData>
+  <dataConsolidate/>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="5">
     <dataValidation showInputMessage="1" showErrorMessage="1" sqref="A1:A1048576" xr:uid="{8C7B18EB-1706-4693-9E43-8A9FE2C13F13}"/>

--- a/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsBuildSchemeList.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsBuildSchemeList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-sp\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC93801E-5859-45D7-AD2A-DF6550564114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7777C6B-A9C3-4A00-BA92-78BE4FA77F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023-07-05" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>方案分级</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -44,25 +44,20 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>计划编制完成时间
+    <t>方案名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否危大工程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施工重难点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>变更类型
 （版本调整时必填）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>方案名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否危大工程</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>施工重难点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>变更类型
-（版本调整时填写）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -164,7 +159,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -190,9 +185,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -476,26 +468,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.875" customWidth="1"/>
-    <col min="2" max="2" width="20.125" customWidth="1"/>
-    <col min="3" max="3" width="33.5" customWidth="1"/>
-    <col min="4" max="4" width="28.75" customWidth="1"/>
-    <col min="5" max="5" width="12.75" customWidth="1"/>
-    <col min="6" max="6" width="21.5" customWidth="1"/>
+    <col min="1" max="1" width="25.88671875" customWidth="1"/>
+    <col min="2" max="2" width="20.109375" customWidth="1"/>
+    <col min="3" max="3" width="33.44140625" customWidth="1"/>
+    <col min="4" max="4" width="28.77734375" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" customWidth="1"/>
     <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="23.5" style="2" customWidth="1"/>
-    <col min="9" max="10" width="26.125" customWidth="1"/>
+    <col min="8" max="8" width="23.44140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="26.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="33" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>9</v>
+        <v>5</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>1</v>
@@ -507,10 +499,10 @@
         <v>0</v>
       </c>
       <c r="F1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>7</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>8</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>4</v>
@@ -518,16 +510,13 @@
       <c r="I1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="8" t="s">
-        <v>5</v>
-      </c>
     </row>
-    <row r="2" spans="1:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:9" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H7" s="3"/>
     </row>
   </sheetData>
@@ -544,7 +533,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F1048576" xr:uid="{3F6E782B-132D-4291-996A-5A482D0F5A7E}">
       <formula1>"一般,危大,超危大"</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H1048576 I1:I1048576 J1:J1048576" xr:uid="{04CC7526-2AAB-4B71-A3DC-4971EBCC8533}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H1048576 I1:I1048576" xr:uid="{04CC7526-2AAB-4B71-A3DC-4971EBCC8533}">
       <formula1>18172</formula1>
       <formula2>383415</formula2>
     </dataValidation>

--- a/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsBuildSchemeList.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsBuildSchemeList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-sp\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7777C6B-A9C3-4A00-BA92-78BE4FA77F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D2EDADA-8089-45F4-8725-1C666FBED0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,11 +39,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>计划实施时间
-（版本V1.0时必填）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>方案名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -58,6 +53,11 @@
   <si>
     <t>变更类型
 （版本调整时必填）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划实施时间
+（首次导入时必填）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -484,10 +484,10 @@
   <sheetData>
     <row r="1" spans="1:9" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>1</v>
@@ -499,13 +499,13 @@
         <v>0</v>
       </c>
       <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>7</v>
-      </c>
       <c r="H1" s="6" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I1" s="8" t="s">
         <v>3</v>
@@ -533,7 +533,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F1048576" xr:uid="{3F6E782B-132D-4291-996A-5A482D0F5A7E}">
       <formula1>"一般,危大,超危大"</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H1048576 I1:I1048576" xr:uid="{04CC7526-2AAB-4B71-A3DC-4971EBCC8533}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I1048576" xr:uid="{04CC7526-2AAB-4B71-A3DC-4971EBCC8533}">
       <formula1>18172</formula1>
       <formula2>383415</formula2>
     </dataValidation>
